--- a/ranking/treemap-country.xlsx
+++ b/ranking/treemap-country.xlsx
@@ -8,27 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bumjunekim/Desktop/qubit-data-processing/ranking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B7577B-F9F0-0D4F-89CE-F8B728D15AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C86A2E-C30E-6B4A-9E77-7768E5A1CFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="760" windowWidth="34160" windowHeight="20100" activeTab="1" xr2:uid="{B9389278-CF75-3349-A542-B7CABE5F4B4F}"/>
+    <workbookView xWindow="160" yWindow="760" windowWidth="34160" windowHeight="20100" activeTab="1" xr2:uid="{B9389278-CF75-3349-A542-B7CABE5F4B4F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="country" sheetId="2" r:id="rId1"/>
+    <sheet name="institution" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$1:$B$50</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$C$1:$C$50</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Sheet1 (2)'!$A$1:$B$40</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Sheet1 (2)'!$C$1:$C$40</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$A$1:$B$50</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$C$1:$C$50</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$A$1:$B$50</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$C$1:$C$50</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'Sheet1 (2)'!$A$1:$B$40</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'Sheet1 (2)'!$C$1:$C$40</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'Sheet1 (2)'!$A$1:$B$40</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Sheet1 (2)'!$C$1:$C$40</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">country!$A$1:$B$40</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">country!$C$1:$C$40</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">country!$A$1:$B$40</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">country!$C$1:$C$40</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">institution!$A$1:$B$40</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">institution!$C$1:$C$40</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">country!$A$1:$B$40</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">country!$C$1:$C$40</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">country!$A$1:$B$40</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">country!$C$1:$C$40</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">country!$A$1:$B$40</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">country!$C$1:$C$40</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">country!$A$1:$B$40</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">country!$C$1:$C$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>Superconducting</t>
   </si>
@@ -65,9 +67,6 @@
     <t>Photonic</t>
   </si>
   <si>
-    <t>Neutral-Atom</t>
-  </si>
-  <si>
     <t>US</t>
   </si>
   <si>
@@ -113,10 +112,85 @@
     <t>IT</t>
   </si>
   <si>
-    <t>SG</t>
-  </si>
-  <si>
-    <t>KR</t>
+    <t>Chinese Acad Sci</t>
+  </si>
+  <si>
+    <t>Yale Univ</t>
+  </si>
+  <si>
+    <t>Univ Sci &amp; Technol China</t>
+  </si>
+  <si>
+    <t>RIKEN</t>
+  </si>
+  <si>
+    <t>MIT</t>
+  </si>
+  <si>
+    <t>Tsinghua Univ</t>
+  </si>
+  <si>
+    <t>Delft Univ Technol</t>
+  </si>
+  <si>
+    <t>Nanjing Univ</t>
+  </si>
+  <si>
+    <t>Univ Calif Santa Barbara</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
+    <t>Univ Innsbruck</t>
+  </si>
+  <si>
+    <t>Univ Maryland</t>
+  </si>
+  <si>
+    <t>Austrian Acad Sci</t>
+  </si>
+  <si>
+    <t>Univ Oxford</t>
+  </si>
+  <si>
+    <t>Duke Univ</t>
+  </si>
+  <si>
+    <t>IonQ Inc</t>
+  </si>
+  <si>
+    <t>Quantinuum</t>
+  </si>
+  <si>
+    <t>Harvard Univ</t>
+  </si>
+  <si>
+    <t>Univ New South Wales</t>
+  </si>
+  <si>
+    <t>Univ Basel</t>
+  </si>
+  <si>
+    <t>Univ Grenoble Alpes</t>
+  </si>
+  <si>
+    <t>Univ Konstanz</t>
+  </si>
+  <si>
+    <t>Rhein Westfal TH Aachen</t>
+  </si>
+  <si>
+    <t>Univ Chicago</t>
+  </si>
+  <si>
+    <t>Univ Vienna</t>
+  </si>
+  <si>
+    <t>Univ Bristol</t>
+  </si>
+  <si>
+    <t>Natl Univ Singapore</t>
   </si>
 </sst>
 </file>
@@ -160,11 +234,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -187,45 +261,48 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:strDim>
       <cx:numDim type="size">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap" uniqueId="{D9A135E1-8CC1-E843-ADD8-DFA526EE6384}">
-          <cx:dataLabels pos="ctr">
-            <cx:spPr>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </cx:spPr>
+        <cx:series layoutId="treemap" uniqueId="{3F6E23E9-09A9-6C4D-B98A-8E9CAF34D598}">
+          <cx:dataLabels pos="inEnd">
             <cx:txPr>
               <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr algn="ctr" rtl="0">
-                  <a:defRPr sz="2300">
+                  <a:defRPr sz="1400">
                     <a:ln>
-                      <a:noFill/>
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
                     </a:ln>
                     <a:solidFill>
-                      <a:sysClr val="window" lastClr="FFFFFF"/>
+                      <a:schemeClr val="bg1"/>
                     </a:solidFill>
+                    <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US" sz="2300" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:endParaRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:ln>
-                    <a:noFill/>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
                   </a:ln>
                   <a:solidFill>
-                    <a:sysClr val="window" lastClr="FFFFFF"/>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
-                  <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+                  <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
                 </a:endParaRPr>
               </a:p>
             </cx:txPr>
@@ -238,25 +315,148 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr algn="ctr" rtl="0">
-                    <a:defRPr/>
+                    <a:defRPr sz="1800">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="accent4"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                       <a:ln>
-                        <a:noFill/>
+                        <a:solidFill>
+                          <a:schemeClr val="accent4"/>
+                        </a:solidFill>
                       </a:ln>
                       <a:solidFill>
-                        <a:sysClr val="window" lastClr="FFFFFF"/>
+                        <a:schemeClr val="accent4"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
                     </a:rPr>
                     <a:t>Superconducting</a:t>
                   </a:r>
                 </a:p>
               </cx:txPr>
-              <cx:visibility seriesName="0" categoryName="1" value="1"/>
-              <cx:separator>
-</cx:separator>
+              <cx:visibility seriesName="0" categoryName="1" value="0"/>
+            </cx:dataLabel>
+            <cx:dataLabel idx="11">
+              <cx:txPr>
+                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr" rtl="0">
+                    <a:defRPr sz="1800">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    </a:rPr>
+                    <a:t>Trapped-Ion</a:t>
+                  </a:r>
+                </a:p>
+              </cx:txPr>
+            </cx:dataLabel>
+            <cx:dataLabel idx="22">
+              <cx:txPr>
+                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr" rtl="0">
+                    <a:defRPr sz="1800">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    </a:rPr>
+                    <a:t>Spin</a:t>
+                  </a:r>
+                </a:p>
+              </cx:txPr>
+            </cx:dataLabel>
+            <cx:dataLabel idx="33">
+              <cx:txPr>
+                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr" rtl="0">
+                    <a:defRPr sz="1800">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="accent5">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent5">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="accent5">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent5">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    </a:rPr>
+                    <a:t>Photonic</a:t>
+                  </a:r>
+                </a:p>
+              </cx:txPr>
             </cx:dataLabel>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -267,14 +467,6 @@
       </cx:plotAreaRegion>
     </cx:plotArea>
   </cx:chart>
-  <cx:spPr>
-    <a:ln cap="flat">
-      <a:solidFill>
-        <a:schemeClr val="accent1"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </cx:spPr>
 </cx:chartSpace>
 </file>
 
@@ -283,48 +475,199 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.10</cx:f>
+        <cx:f>_xlchart.v1.12</cx:f>
       </cx:strDim>
       <cx:numDim type="size">
-        <cx:f>_xlchart.v1.11</cx:f>
+        <cx:f>_xlchart.v1.13</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0"/>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap" uniqueId="{776587DF-936B-AD4F-85F5-CE24940A5CE6}">
-          <cx:dataPt idx="22"/>
-          <cx:dataLabels pos="ctr">
-            <cx:numFmt formatCode="General" sourceLinked="0"/>
+        <cx:series layoutId="treemap" uniqueId="{3F6E23E9-09A9-6C4D-B98A-8E9CAF34D598}">
+          <cx:dataLabels pos="inEnd">
             <cx:txPr>
               <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr algn="ctr" rtl="0">
                   <a:defRPr sz="1400">
+                    <a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                    </a:ln>
                     <a:solidFill>
-                      <a:sysClr val="window" lastClr="FFFFFF"/>
+                      <a:schemeClr val="bg1"/>
                     </a:solidFill>
+                    <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    <a:ea typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:ln>
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:ln>
                   <a:solidFill>
-                    <a:sysClr val="window" lastClr="FFFFFF"/>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
-                  <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+                  <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                  <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
                 </a:endParaRPr>
               </a:p>
             </cx:txPr>
             <cx:visibility seriesName="0" categoryName="1" value="1"/>
             <cx:separator>
 </cx:separator>
-            <cx:dataLabel idx="11">
-              <cx:numFmt formatCode="General" sourceLinked="0"/>
-              <cx:visibility seriesName="0" categoryName="1" value="1"/>
+            <cx:dataLabel idx="0">
+              <cx:txPr>
+                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr" rtl="0">
+                    <a:defRPr sz="2000">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="accent4"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="accent4"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    </a:rPr>
+                    <a:t>Superconducting</a:t>
+                  </a:r>
+                </a:p>
+              </cx:txPr>
+              <cx:visibility seriesName="0" categoryName="1" value="0"/>
               <cx:separator>
 </cx:separator>
+            </cx:dataLabel>
+            <cx:dataLabel idx="11">
+              <cx:txPr>
+                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr" rtl="0">
+                    <a:defRPr sz="2000"/>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    </a:rPr>
+                    <a:t>Trapped-Ion</a:t>
+                  </a:r>
+                </a:p>
+              </cx:txPr>
+            </cx:dataLabel>
+            <cx:dataLabel idx="22">
+              <cx:txPr>
+                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr" rtl="0">
+                    <a:defRPr sz="2000">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="bg2">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="bg2">
+                          <a:lumMod val="10000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    </a:rPr>
+                    <a:t>Spin</a:t>
+                  </a:r>
+                </a:p>
+              </cx:txPr>
+            </cx:dataLabel>
+            <cx:dataLabel idx="33">
+              <cx:txPr>
+                <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr algn="ctr" rtl="0">
+                    <a:defRPr sz="2000">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="accent5">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent5">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                      <a:ln>
+                        <a:solidFill>
+                          <a:schemeClr val="accent5">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                      </a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent5">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                      <a:cs typeface="Telugu Sangam MN" pitchFamily="2" charset="0"/>
+                    </a:rPr>
+                    <a:t>Photonic</a:t>
+                  </a:r>
+                </a:p>
+              </cx:txPr>
             </cx:dataLabel>
           </cx:dataLabels>
           <cx:dataId val="0"/>
@@ -419,7 +762,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="416">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="410">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -436,7 +779,7 @@
           <a:lumMod val="65000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln>
+      <a:ln w="19050">
         <a:solidFill>
           <a:schemeClr val="bg1"/>
         </a:solidFill>
@@ -497,7 +840,7 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1000" b="1"/>
+    <cs:defRPr sz="900"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -540,7 +883,7 @@
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:ln>
+      <a:ln w="19050">
         <a:solidFill>
           <a:schemeClr val="lt1"/>
         </a:solidFill>
@@ -600,7 +943,7 @@
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -775,6 +1118,17 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
@@ -853,7 +1207,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" cap="all"/>
+    <cs:defRPr sz="1400"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -930,7 +1284,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="416">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="410">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -947,7 +1301,7 @@
           <a:lumMod val="65000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln>
+      <a:ln w="19050">
         <a:solidFill>
           <a:schemeClr val="bg1"/>
         </a:solidFill>
@@ -1008,7 +1362,7 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1000" b="1"/>
+    <cs:defRPr sz="900"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -1051,7 +1405,7 @@
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:ln>
+      <a:ln w="19050">
         <a:solidFill>
           <a:schemeClr val="lt1"/>
         </a:solidFill>
@@ -1111,7 +1465,7 @@
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -1286,6 +1640,17 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
@@ -1364,7 +1729,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" cap="all"/>
+    <cs:defRPr sz="1400"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1444,31 +1809,29 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>250825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>572154</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="4" name="Chart 3">
+            <xdr:cNvPr id="2" name="Chart 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1370F9F7-AF15-B31D-4066-6E1A1691CCD6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB3D005C-2267-9A4A-A805-306950173244}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr>
-              <a:graphicFrameLocks noChangeAspect="1"/>
-            </xdr:cNvGraphicFramePr>
+            <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
             <a:off x="0" y="0"/>
@@ -1491,8 +1854,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4441825" y="3429000"/>
-              <a:ext cx="37202129" cy="14859000"/>
+              <a:off x="2749550" y="565150"/>
+              <a:ext cx="18408650" cy="8477250"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1530,24 +1893,24 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>258937</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>45860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>506588</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>186266</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Chart 2">
+            <xdr:cNvPr id="2" name="Chart 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{948EA89E-8AA0-87EB-EF30-6A252E6B7A94}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E84E7D-7737-894E-A53E-602FCE78922E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1574,8 +1937,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4159250" y="781050"/>
-              <a:ext cx="12630150" cy="7029450"/>
+              <a:off x="4421715" y="243416"/>
+              <a:ext cx="18563873" cy="8240183"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1904,477 +2267,384 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5488F23A-22A4-504D-98E8-88EAC43B3322}">
-  <dimension ref="A1:C50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F408364-4C1B-584A-B663-7E81360AF637}">
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="3">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="1">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="1">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="1">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="C15" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="2">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
+      <c r="C23" s="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
+      <c r="C28" s="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="C36" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="2">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2" t="s">
+      <c r="C38" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="2">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="2">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
-      <c r="B38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="2">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="C39" s="1">
         <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="2">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="1">
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
-      <c r="B50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="2">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:A10"/>
     <mergeCell ref="A11:A20"/>
     <mergeCell ref="A21:A30"/>
     <mergeCell ref="A31:A40"/>
-    <mergeCell ref="A41:A50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2383,376 +2653,376 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F408364-4C1B-584A-B663-7E81360AF637}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FBF49C-4A25-D54E-A2C1-4176D724ADC2}">
   <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="3">
-        <v>1351</v>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1">
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2">
-        <v>877</v>
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1">
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2">
-        <v>408</v>
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1">
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2">
-        <v>325</v>
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1">
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
-        <v>304</v>
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2">
-        <v>230</v>
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1">
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>202</v>
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1">
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2">
-        <v>179</v>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2">
-        <v>173</v>
+      <c r="A9" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1">
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="2">
-        <v>145</v>
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2">
-        <v>239</v>
+      <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1">
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2">
-        <v>83</v>
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2">
-        <v>73</v>
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="2">
-        <v>65</v>
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2">
-        <v>59</v>
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2">
-        <v>32</v>
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="2">
-        <v>27</v>
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="1">
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="2">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="2">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="2">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2">
-        <v>66</v>
-      </c>
-    </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-      <c r="B37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2">
-        <v>65</v>
+      <c r="A37" s="2"/>
+      <c r="B37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="1">
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
-      <c r="B38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="2">
-        <v>63</v>
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="1">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="2">
-        <v>62</v>
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="1">
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="2">
-        <v>56</v>
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="1">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
